--- a/Test/ユーザー登録 確認＆完了結合テストケース実行.xlsx
+++ b/Test/ユーザー登録 確認＆完了結合テストケース実行.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="259">
   <si>
     <t>テストID</t>
   </si>
@@ -311,6 +311,11 @@
     <t>完了画面に遷移し、データベースの「password」の欄にハッシュ化されたパスワードが表示される。</t>
   </si>
   <si>
+    <t>登録パスワード：Hatune39
+データベース内：$2y$10$C4Z/cZEhaJROlT.Db3TIxuZYjQyqJvFGgObwwG8zFpI...
+完了画面に遷移し、上記の内容でハッシュ化されたパスワードがデータベースに登録された。</t>
+  </si>
+  <si>
     <t>UT-006</t>
   </si>
   <si>
@@ -355,6 +360,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「北海道」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「北海道」が表示された。</t>
+  </si>
+  <si>
     <t>UT-007</t>
   </si>
   <si>
@@ -399,6 +407,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「青森県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「青森県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-008</t>
   </si>
   <si>
@@ -443,6 +454,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「岩手県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「岩手県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-009</t>
   </si>
   <si>
@@ -487,6 +501,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「宮城県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「宮城県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-010</t>
   </si>
   <si>
@@ -531,6 +548,9 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「秋田県」が表示される。</t>
   </si>
   <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「秋田県」が表示された。</t>
+  </si>
+  <si>
     <t>UT-011</t>
   </si>
   <si>
@@ -564,7 +584,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝福島県
+      <t>＝山形県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -572,7 +592,10 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「福島県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山形県」が表示される。</t>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山形県」が表示された。</t>
   </si>
   <si>
     <t>UT-012</t>
@@ -608,7 +631,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝茨城県
+      <t>＝福島県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -616,7 +639,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「茨城県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「福島県」が表示される。</t>
   </si>
   <si>
     <t>UT-013</t>
@@ -652,7 +675,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝栃木県
+      <t>＝茨城県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -660,7 +683,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「栃木県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「茨城県」が表示される。</t>
   </si>
   <si>
     <t>UT-014</t>
@@ -696,7 +719,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝群馬県
+      <t>＝栃木県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -704,7 +727,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「群馬県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「栃木県」が表示される。</t>
   </si>
   <si>
     <t>UT-015</t>
@@ -740,7 +763,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝埼玉県
+      <t>＝群馬県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -748,7 +771,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「埼玉県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「群馬県」が表示される。</t>
   </si>
   <si>
     <t>UT-016</t>
@@ -784,7 +807,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝千葉県
+      <t>＝埼玉県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -792,7 +815,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「千葉県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「埼玉県」が表示される。</t>
   </si>
   <si>
     <t>UT-017</t>
@@ -828,7 +851,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝東京都
+      <t>＝千葉県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -836,7 +859,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「東京都」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「千葉県」が表示される。</t>
   </si>
   <si>
     <t>UT-018</t>
@@ -872,7 +895,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝神奈川県
+      <t>＝東京都
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -880,7 +903,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「神奈川県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「東京都」が表示される。</t>
   </si>
   <si>
     <t>UT-019</t>
@@ -916,7 +939,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝新潟県
+      <t>＝神奈川県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -924,7 +947,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「新潟県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「神奈川県」が表示される。</t>
   </si>
   <si>
     <t>UT-020</t>
@@ -960,7 +983,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝石川県
+      <t>＝新潟県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -968,7 +991,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「石川県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「新潟県」が表示される。</t>
   </si>
   <si>
     <t>UT-021</t>
@@ -1004,7 +1027,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝福井県
+      <t>＝石川県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1012,7 +1035,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「福井県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「石川県」が表示される。</t>
   </si>
   <si>
     <t>UT-022</t>
@@ -1048,7 +1071,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝山梨県
+      <t>＝福井県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1056,7 +1079,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「山梨県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「福井県」が表示される。</t>
   </si>
   <si>
     <t>UT-023</t>
@@ -1092,7 +1115,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝長野県
+      <t>＝山梨県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1100,7 +1123,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「長野県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山梨県」が表示される。</t>
   </si>
   <si>
     <t>UT-024</t>
@@ -1136,7 +1159,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝岐阜県
+      <t>＝長野県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1144,7 +1167,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「岐阜県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「長野県」が表示される。</t>
   </si>
   <si>
     <t>UT-025</t>
@@ -1180,7 +1203,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝静岡県
+      <t>＝岐阜県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1188,7 +1211,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「静岡県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「岐阜県」が表示される。</t>
   </si>
   <si>
     <t>UT-026</t>
@@ -1224,7 +1247,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝愛知県
+      <t>＝静岡県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1232,7 +1255,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「愛知県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「静岡県」が表示される。</t>
   </si>
   <si>
     <t>UT-027</t>
@@ -1268,7 +1291,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝三重県
+      <t>＝愛知県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1276,7 +1299,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「三重県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「愛知県」が表示される。</t>
   </si>
   <si>
     <t>UT-028</t>
@@ -1312,7 +1335,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝滋賀県
+      <t>＝三重県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1320,7 +1343,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「滋賀県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「三重県」が表示される。</t>
   </si>
   <si>
     <t>UT-029</t>
@@ -1356,7 +1379,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝京都府
+      <t>＝滋賀県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1364,7 +1387,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「京都府」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「滋賀県」が表示される。</t>
   </si>
   <si>
     <t>UT-030</t>
@@ -1400,7 +1423,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝大阪府
+      <t>＝京都府
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1408,7 +1431,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「大阪府」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「京都府」が表示される。</t>
   </si>
   <si>
     <t>UT-031</t>
@@ -1444,7 +1467,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝兵庫県
+      <t>＝大阪府
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1452,7 +1475,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「兵庫県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「大阪府」が表示される。</t>
   </si>
   <si>
     <t>UT-032</t>
@@ -1488,7 +1511,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝和歌山県
+      <t>＝兵庫県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1496,7 +1519,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「和歌山県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「兵庫県」が表示される。</t>
   </si>
   <si>
     <t>UT-033</t>
@@ -1532,7 +1555,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝鳥取県
+      <t>＝和歌山県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1540,7 +1563,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「鳥取県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「和歌山県」が表示される。</t>
   </si>
   <si>
     <t>UT-034</t>
@@ -1576,7 +1599,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝島根県
+      <t>＝鳥取県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1584,7 +1607,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「島根県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「鳥取県」が表示される。</t>
   </si>
   <si>
     <t>UT-035</t>
@@ -1620,7 +1643,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝岡山県
+      <t>＝島根県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1628,7 +1651,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「岡山県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「島根県」が表示される。</t>
   </si>
   <si>
     <t>UT-036</t>
@@ -1664,7 +1687,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝広島県
+      <t>＝岡山県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1672,7 +1695,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「広島県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「岡山県」が表示される。</t>
   </si>
   <si>
     <t>UT-037</t>
@@ -1708,7 +1731,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝山口県
+      <t>＝広島県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1716,7 +1739,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「山口県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「広島県」が表示される。</t>
   </si>
   <si>
     <t>UT-038</t>
@@ -1752,7 +1775,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝徳島県
+      <t>＝山口県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1760,7 +1783,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「徳島県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「山口県」が表示される。</t>
   </si>
   <si>
     <t>UT-039</t>
@@ -1796,7 +1819,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝愛媛県
+      <t>＝徳島県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1804,7 +1827,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「愛媛県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「徳島県」が表示される。</t>
   </si>
   <si>
     <t>UT-040</t>
@@ -1840,7 +1863,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝香川県
+      <t>＝愛媛県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1848,7 +1871,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「香川県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「愛媛県」が表示される。</t>
   </si>
   <si>
     <t>UT-041</t>
@@ -1884,7 +1907,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝高知県
+      <t>＝香川県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1892,7 +1915,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「高知県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「香川県」が表示される。</t>
   </si>
   <si>
     <t>UT-042</t>
@@ -1928,7 +1951,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝福岡県
+      <t>＝高知県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1936,7 +1959,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「福岡県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「高知県」が表示される。</t>
   </si>
   <si>
     <t>UT-043</t>
@@ -1972,7 +1995,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝佐賀県
+      <t>＝福岡県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -1980,7 +2003,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「佐賀県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「福岡県」が表示される。</t>
   </si>
   <si>
     <t>UT-044</t>
@@ -2016,7 +2039,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝長崎県
+      <t>＝佐賀県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -2024,7 +2047,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「長崎県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「佐賀県」が表示される。</t>
   </si>
   <si>
     <t>UT-045</t>
@@ -2060,7 +2083,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝熊本県
+      <t>＝長崎県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -2068,7 +2091,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「熊本県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「長崎県」が表示される。</t>
   </si>
   <si>
     <t>UT-046</t>
@@ -2104,7 +2127,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝大分県
+      <t>＝熊本県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -2112,10 +2135,10 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「大分県」が表示される。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UT-047 </t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「熊本県」が表示される。</t>
+  </si>
+  <si>
+    <t>UT-047</t>
   </si>
   <si>
     <r>
@@ -2148,7 +2171,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝宮崎県
+      <t>＝大分県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -2156,7 +2179,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「宮崎県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「大分県」が表示される。</t>
   </si>
   <si>
     <t>UT-048</t>
@@ -2192,7 +2215,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>＝鹿児島県
+      <t>＝宮崎県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
 アカウント権限＝一般か管理者を選択
@@ -2200,7 +2223,7 @@
     </r>
   </si>
   <si>
-    <t>完了画面に遷移し、データベースの都道府県の欄に「鹿児島県」が表示される。</t>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「宮崎県」が表示される。</t>
   </si>
   <si>
     <t>UT-049</t>
@@ -2236,6 +2259,50 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
+      <t>＝鹿児島県
+住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
+住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
+アカウント権限＝一般か管理者を選択
+（※登録画面にて入力する内容）"</t>
+    </r>
+  </si>
+  <si>
+    <t>完了画面に遷移し、データベースの都道府県の欄に「鹿児島県」が表示される。</t>
+  </si>
+  <si>
+    <t>UT-050</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">"名前（姓）=ひらがな・漢字・10文字以内
+名前（名）=ひらがな・漢字・10文字以内
+カナ（姓）=カタカナ・10文字以内
+カナ（名）=カタカナ・10文字以内
+メールアドレス=半角英数字・半角記号（ハイフン・アットマーク）・100文字以内
+パスワード=半角英数字・10文字以内
+性別＝男か女のどちらかを選択
+郵便番号=半角数字・7文字以内
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>住所（都道府県）</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
       <t>＝沖縄県
 住所（市区町村）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・10文字
 住所（番地）=ひらがな・漢字・カタカナ・数字・記号（ハイフン・スペース）のみ・100文字
@@ -2247,7 +2314,7 @@
     <t>完了画面に遷移し、データベースの都道府県の欄に「沖縄県」が表示される。</t>
   </si>
   <si>
-    <t>UT-050</t>
+    <t>UT-051</t>
   </si>
   <si>
     <t>"名前（姓）=ひらがな・漢字・10文字以内
@@ -2595,7 +2662,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -2634,11 +2701,6 @@
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
       <left/>
       <top/>
       <bottom/>
@@ -2656,7 +2718,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2681,23 +2743,17 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -3166,15 +3222,23 @@
       <c r="H6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="I6" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>14</v>
@@ -3189,23 +3253,31 @@
         <v>29</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="I7" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>14</v>
@@ -3220,23 +3292,31 @@
         <v>29</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="I8" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>14</v>
@@ -3251,23 +3331,31 @@
         <v>29</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="I9" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>14</v>
@@ -3282,23 +3370,31 @@
         <v>29</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="I10" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>14</v>
@@ -3313,23 +3409,31 @@
         <v>29</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="I11" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>14</v>
@@ -3344,23 +3448,31 @@
         <v>29</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="I12" s="5">
+        <v>46154.0</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>14</v>
@@ -3375,10 +3487,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>20</v>
@@ -3391,7 +3503,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
@@ -3406,10 +3518,10 @@
         <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>20</v>
@@ -3422,7 +3534,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>14</v>
@@ -3437,10 +3549,10 @@
         <v>29</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>20</v>
@@ -3453,7 +3565,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>14</v>
@@ -3468,10 +3580,10 @@
         <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>20</v>
@@ -3484,7 +3596,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>14</v>
@@ -3499,10 +3611,10 @@
         <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>20</v>
@@ -3515,7 +3627,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>14</v>
@@ -3530,10 +3642,10 @@
         <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>20</v>
@@ -3546,7 +3658,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>14</v>
@@ -3561,10 +3673,10 @@
         <v>29</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>20</v>
@@ -3577,7 +3689,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>14</v>
@@ -3592,10 +3704,10 @@
         <v>29</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>20</v>
@@ -3608,7 +3720,7 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>14</v>
@@ -3623,10 +3735,10 @@
         <v>29</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>20</v>
@@ -3639,7 +3751,7 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>14</v>
@@ -3654,10 +3766,10 @@
         <v>29</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>20</v>
@@ -3670,7 +3782,7 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>14</v>
@@ -3685,10 +3797,10 @@
         <v>29</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>20</v>
@@ -3701,7 +3813,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>14</v>
@@ -3716,10 +3828,10 @@
         <v>29</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>20</v>
@@ -3732,7 +3844,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>14</v>
@@ -3747,10 +3859,10 @@
         <v>29</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>20</v>
@@ -3763,7 +3875,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>14</v>
@@ -3778,10 +3890,10 @@
         <v>29</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>20</v>
@@ -3794,7 +3906,7 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>14</v>
@@ -3809,10 +3921,10 @@
         <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>20</v>
@@ -3825,7 +3937,7 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>14</v>
@@ -3840,10 +3952,10 @@
         <v>29</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>20</v>
@@ -3856,7 +3968,7 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>14</v>
@@ -3871,10 +3983,10 @@
         <v>29</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>20</v>
@@ -3887,7 +3999,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>14</v>
@@ -3902,10 +4014,10 @@
         <v>29</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>20</v>
@@ -3918,7 +4030,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>14</v>
@@ -3933,10 +4045,10 @@
         <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>20</v>
@@ -3949,7 +4061,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>14</v>
@@ -3964,10 +4076,10 @@
         <v>29</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>20</v>
@@ -3980,7 +4092,7 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>14</v>
@@ -3995,10 +4107,10 @@
         <v>29</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>20</v>
@@ -4011,7 +4123,7 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>14</v>
@@ -4026,10 +4138,10 @@
         <v>29</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>20</v>
@@ -4042,7 +4154,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>14</v>
@@ -4057,10 +4169,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>20</v>
@@ -4073,7 +4185,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>14</v>
@@ -4088,10 +4200,10 @@
         <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>20</v>
@@ -4104,7 +4216,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>14</v>
@@ -4119,10 +4231,10 @@
         <v>29</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>20</v>
@@ -4135,7 +4247,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>14</v>
@@ -4150,10 +4262,10 @@
         <v>29</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>20</v>
@@ -4166,7 +4278,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>14</v>
@@ -4181,10 +4293,10 @@
         <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>20</v>
@@ -4197,7 +4309,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>14</v>
@@ -4212,10 +4324,10 @@
         <v>29</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>20</v>
@@ -4228,7 +4340,7 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>14</v>
@@ -4243,10 +4355,10 @@
         <v>29</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>20</v>
@@ -4259,7 +4371,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>14</v>
@@ -4274,10 +4386,10 @@
         <v>29</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>20</v>
@@ -4290,7 +4402,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>14</v>
@@ -4305,10 +4417,10 @@
         <v>29</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>20</v>
@@ -4321,7 +4433,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>14</v>
@@ -4336,10 +4448,10 @@
         <v>29</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>20</v>
@@ -4352,7 +4464,7 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>14</v>
@@ -4367,10 +4479,10 @@
         <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>20</v>
@@ -4383,7 +4495,7 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>14</v>
@@ -4398,10 +4510,10 @@
         <v>29</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>20</v>
@@ -4414,7 +4526,7 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>14</v>
@@ -4429,10 +4541,10 @@
         <v>29</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>20</v>
@@ -4445,7 +4557,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>14</v>
@@ -4460,10 +4572,10 @@
         <v>29</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>20</v>
@@ -4476,7 +4588,7 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>14</v>
@@ -4491,10 +4603,10 @@
         <v>29</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>20</v>
@@ -4507,7 +4619,7 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>14</v>
@@ -4522,10 +4634,10 @@
         <v>29</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>20</v>
@@ -4537,80 +4649,96 @@
       <c r="M50" s="2"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H51" s="7" t="s">
+      <c r="F51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
+      <c r="A52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
     </row>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
@@ -4635,7 +4763,7 @@
     <row r="75" ht="15.75" customHeight="1"/>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>14</v>
@@ -4650,10 +4778,10 @@
         <v>29</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>20</v>
@@ -5612,13 +5740,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -5626,181 +5754,181 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -6807,25 +6935,25 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
+      <c r="A1" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>204</v>
+      <c r="A3" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -6833,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5">
@@ -6847,13 +6975,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
@@ -6861,13 +6989,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
@@ -6875,13 +7003,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
@@ -6889,27 +7017,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -6917,13 +7045,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6931,13 +7059,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
@@ -6945,13 +7073,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
@@ -6959,13 +7087,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -6973,13 +7101,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
@@ -6987,13 +7115,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
@@ -7001,58 +7129,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="s">
-        <v>242</v>
+      <c r="A18" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>244</v>
+      <c r="A19" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>245</v>
+      <c r="A20" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>246</v>
+      <c r="A21" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>247</v>
+      <c r="A22" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>248</v>
+      <c r="A23" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
